--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127843091</v>
       </c>
       <c r="B2" t="n">
-        <v>97482</v>
+        <v>97485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127843067</v>
       </c>
       <c r="B3" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127843092</v>
       </c>
       <c r="B4" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843088</v>
+        <v>127843093</v>
       </c>
       <c r="B5" t="n">
-        <v>91356</v>
+        <v>100641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445253</v>
+        <v>445181</v>
       </c>
       <c r="R5" t="n">
-        <v>7039001</v>
+        <v>7038904</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843093</v>
+        <v>127843088</v>
       </c>
       <c r="B6" t="n">
-        <v>100638</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445181</v>
+        <v>445253</v>
       </c>
       <c r="R6" t="n">
-        <v>7038904</v>
+        <v>7039001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127843080</v>
       </c>
       <c r="B7" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843094</v>
+        <v>127843090</v>
       </c>
       <c r="B8" t="n">
-        <v>100638</v>
+        <v>97485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445285</v>
+        <v>445194</v>
       </c>
       <c r="R8" t="n">
-        <v>7039016</v>
+        <v>7039028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843090</v>
+        <v>127843094</v>
       </c>
       <c r="B9" t="n">
-        <v>97482</v>
+        <v>100641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445194</v>
+        <v>445285</v>
       </c>
       <c r="R9" t="n">
-        <v>7039028</v>
+        <v>7039016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>127843086</v>
       </c>
       <c r="B10" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127843084</v>
       </c>
       <c r="B11" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127843082</v>
       </c>
       <c r="B12" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127843083</v>
       </c>
       <c r="B13" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127843095</v>
       </c>
       <c r="B14" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127843081</v>
       </c>
       <c r="B15" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127843072</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>127843070</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>127843074</v>
       </c>
       <c r="B18" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127843071</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127843091</v>
       </c>
       <c r="B2" t="n">
-        <v>97485</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127843067</v>
       </c>
       <c r="B3" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127843092</v>
       </c>
       <c r="B4" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843093</v>
+        <v>127843088</v>
       </c>
       <c r="B5" t="n">
-        <v>100641</v>
+        <v>91367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445181</v>
+        <v>445253</v>
       </c>
       <c r="R5" t="n">
-        <v>7038904</v>
+        <v>7039001</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843088</v>
+        <v>127843093</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>100649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445253</v>
+        <v>445181</v>
       </c>
       <c r="R6" t="n">
-        <v>7039001</v>
+        <v>7038904</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127843080</v>
       </c>
       <c r="B7" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127843090</v>
       </c>
       <c r="B8" t="n">
-        <v>97485</v>
+        <v>97493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127843094</v>
       </c>
       <c r="B9" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127843086</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127843084</v>
       </c>
       <c r="B11" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127843082</v>
       </c>
       <c r="B12" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127843083</v>
       </c>
       <c r="B13" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127843095</v>
       </c>
       <c r="B14" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843081</v>
+        <v>127843072</v>
       </c>
       <c r="B15" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1947,54 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445279</v>
+        <v>445273</v>
       </c>
       <c r="R15" t="n">
-        <v>7039023</v>
+        <v>7039087</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843072</v>
+        <v>127843081</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,54 +2064,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445273</v>
+        <v>445279</v>
       </c>
       <c r="R16" t="n">
-        <v>7039087</v>
+        <v>7039023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
         <v>127843070</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>127843074</v>
       </c>
       <c r="B18" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127843071</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127843091</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127843067</v>
       </c>
       <c r="B3" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127843092</v>
       </c>
       <c r="B4" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127843088</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127843093</v>
       </c>
       <c r="B6" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127843080</v>
       </c>
       <c r="B7" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843090</v>
+        <v>127843094</v>
       </c>
       <c r="B8" t="n">
-        <v>97493</v>
+        <v>100650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445194</v>
+        <v>445285</v>
       </c>
       <c r="R8" t="n">
-        <v>7039028</v>
+        <v>7039016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843094</v>
+        <v>127843090</v>
       </c>
       <c r="B9" t="n">
-        <v>100649</v>
+        <v>97494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445285</v>
+        <v>445194</v>
       </c>
       <c r="R9" t="n">
-        <v>7039016</v>
+        <v>7039028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>127843086</v>
       </c>
       <c r="B10" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127843084</v>
       </c>
       <c r="B11" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127843082</v>
       </c>
       <c r="B12" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127843083</v>
       </c>
       <c r="B13" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127843095</v>
       </c>
       <c r="B14" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127843081</v>
       </c>
       <c r="B16" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127843091</v>
       </c>
       <c r="B2" t="n">
-        <v>97494</v>
+        <v>97495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843067</v>
+        <v>127843092</v>
       </c>
       <c r="B3" t="n">
-        <v>98491</v>
+        <v>100651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445159</v>
+        <v>445157</v>
       </c>
       <c r="R3" t="n">
-        <v>7038937</v>
+        <v>7038934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843092</v>
+        <v>127843067</v>
       </c>
       <c r="B4" t="n">
-        <v>100650</v>
+        <v>98492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445157</v>
+        <v>445159</v>
       </c>
       <c r="R4" t="n">
-        <v>7038934</v>
+        <v>7038937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127843088</v>
       </c>
       <c r="B5" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127843093</v>
       </c>
       <c r="B6" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127843080</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127843094</v>
       </c>
       <c r="B8" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127843090</v>
       </c>
       <c r="B9" t="n">
-        <v>97494</v>
+        <v>97495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127843086</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127843084</v>
       </c>
       <c r="B11" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127843082</v>
       </c>
       <c r="B12" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127843083</v>
       </c>
       <c r="B13" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127843095</v>
       </c>
       <c r="B14" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127843081</v>
       </c>
       <c r="B16" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127843091</v>
       </c>
       <c r="B2" t="n">
-        <v>97495</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127843092</v>
       </c>
       <c r="B3" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127843067</v>
       </c>
       <c r="B4" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843088</v>
+        <v>127843093</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>100652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445253</v>
+        <v>445181</v>
       </c>
       <c r="R5" t="n">
-        <v>7039001</v>
+        <v>7038904</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843093</v>
+        <v>127843088</v>
       </c>
       <c r="B6" t="n">
-        <v>100651</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445181</v>
+        <v>445253</v>
       </c>
       <c r="R6" t="n">
-        <v>7038904</v>
+        <v>7039001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127843080</v>
       </c>
       <c r="B7" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127843094</v>
       </c>
       <c r="B8" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127843090</v>
       </c>
       <c r="B9" t="n">
-        <v>97495</v>
+        <v>97496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127843086</v>
       </c>
       <c r="B10" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127843084</v>
       </c>
       <c r="B11" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127843082</v>
       </c>
       <c r="B12" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127843083</v>
       </c>
       <c r="B13" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127843095</v>
       </c>
       <c r="B14" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127843081</v>
       </c>
       <c r="B16" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843072</v>
+        <v>127843081</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,54 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445273</v>
+        <v>445279</v>
       </c>
       <c r="R15" t="n">
-        <v>7039087</v>
+        <v>7039023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843081</v>
+        <v>127843072</v>
       </c>
       <c r="B16" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,34 +2044,54 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445279</v>
+        <v>445273</v>
       </c>
       <c r="R16" t="n">
-        <v>7039023</v>
+        <v>7039087</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843092</v>
+        <v>127843067</v>
       </c>
       <c r="B3" t="n">
-        <v>100652</v>
+        <v>98493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445157</v>
+        <v>445159</v>
       </c>
       <c r="R3" t="n">
-        <v>7038934</v>
+        <v>7038937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843067</v>
+        <v>127843092</v>
       </c>
       <c r="B4" t="n">
-        <v>98493</v>
+        <v>100652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445159</v>
+        <v>445157</v>
       </c>
       <c r="R4" t="n">
-        <v>7038937</v>
+        <v>7038934</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843067</v>
+        <v>127843092</v>
       </c>
       <c r="B3" t="n">
-        <v>98493</v>
+        <v>100652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445159</v>
+        <v>445157</v>
       </c>
       <c r="R3" t="n">
-        <v>7038937</v>
+        <v>7038934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843092</v>
+        <v>127843067</v>
       </c>
       <c r="B4" t="n">
-        <v>100652</v>
+        <v>98493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445157</v>
+        <v>445159</v>
       </c>
       <c r="R4" t="n">
-        <v>7038934</v>
+        <v>7038937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127843091</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127843067</v>
       </c>
       <c r="B3" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127843092</v>
       </c>
       <c r="B4" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843093</v>
+        <v>127843088</v>
       </c>
       <c r="B5" t="n">
-        <v>100652</v>
+        <v>91378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445181</v>
+        <v>445253</v>
       </c>
       <c r="R5" t="n">
-        <v>7038904</v>
+        <v>7039001</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843088</v>
+        <v>127843093</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>100660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445253</v>
+        <v>445181</v>
       </c>
       <c r="R6" t="n">
-        <v>7039001</v>
+        <v>7038904</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127843080</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127843094</v>
       </c>
       <c r="B8" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127843090</v>
       </c>
       <c r="B9" t="n">
-        <v>97496</v>
+        <v>97504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127843086</v>
       </c>
       <c r="B10" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127843084</v>
       </c>
       <c r="B11" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127843082</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127843083</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127843095</v>
       </c>
       <c r="B14" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843081</v>
+        <v>127843072</v>
       </c>
       <c r="B15" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1947,54 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445279</v>
+        <v>445273</v>
       </c>
       <c r="R15" t="n">
-        <v>7039023</v>
+        <v>7039087</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843072</v>
+        <v>127843081</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,54 +2064,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445273</v>
+        <v>445279</v>
       </c>
       <c r="R16" t="n">
-        <v>7039087</v>
+        <v>7039023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
         <v>127843070</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>127843074</v>
       </c>
       <c r="B18" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127843071</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843072</v>
+        <v>127843081</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,54 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445273</v>
+        <v>445279</v>
       </c>
       <c r="R15" t="n">
-        <v>7039087</v>
+        <v>7039023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843081</v>
+        <v>127843072</v>
       </c>
       <c r="B16" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,34 +2044,54 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445279</v>
+        <v>445273</v>
       </c>
       <c r="R16" t="n">
-        <v>7039023</v>
+        <v>7039087</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127843091</v>
       </c>
       <c r="B2" t="n">
-        <v>97504</v>
+        <v>97597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127843067</v>
       </c>
       <c r="B3" t="n">
-        <v>98501</v>
+        <v>98594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127843092</v>
       </c>
       <c r="B4" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843088</v>
+        <v>127843093</v>
       </c>
       <c r="B5" t="n">
-        <v>91378</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445253</v>
+        <v>445181</v>
       </c>
       <c r="R5" t="n">
-        <v>7039001</v>
+        <v>7038904</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843093</v>
+        <v>127843088</v>
       </c>
       <c r="B6" t="n">
-        <v>100660</v>
+        <v>91470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445181</v>
+        <v>445253</v>
       </c>
       <c r="R6" t="n">
-        <v>7038904</v>
+        <v>7039001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127843080</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127843094</v>
       </c>
       <c r="B8" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127843090</v>
       </c>
       <c r="B9" t="n">
-        <v>97504</v>
+        <v>97597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127843086</v>
       </c>
       <c r="B10" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127843084</v>
       </c>
       <c r="B11" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127843082</v>
       </c>
       <c r="B12" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127843083</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127843095</v>
       </c>
       <c r="B14" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127843081</v>
       </c>
       <c r="B15" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127843072</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>127843070</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>127843074</v>
       </c>
       <c r="B18" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>127843071</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843093</v>
+        <v>127843088</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>91470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445181</v>
+        <v>445253</v>
       </c>
       <c r="R5" t="n">
-        <v>7038904</v>
+        <v>7039001</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843088</v>
+        <v>127843093</v>
       </c>
       <c r="B6" t="n">
-        <v>91470</v>
+        <v>100753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445253</v>
+        <v>445181</v>
       </c>
       <c r="R6" t="n">
-        <v>7039001</v>
+        <v>7038904</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843088</v>
+        <v>127843093</v>
       </c>
       <c r="B5" t="n">
-        <v>91470</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445253</v>
+        <v>445181</v>
       </c>
       <c r="R5" t="n">
-        <v>7039001</v>
+        <v>7038904</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843093</v>
+        <v>127843088</v>
       </c>
       <c r="B6" t="n">
-        <v>100753</v>
+        <v>91470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445181</v>
+        <v>445253</v>
       </c>
       <c r="R6" t="n">
-        <v>7038904</v>
+        <v>7039001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843081</v>
+        <v>127843072</v>
       </c>
       <c r="B15" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1947,54 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445279</v>
+        <v>445273</v>
       </c>
       <c r="R15" t="n">
-        <v>7039023</v>
+        <v>7039087</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843072</v>
+        <v>127843081</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,54 +2064,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445273</v>
+        <v>445279</v>
       </c>
       <c r="R16" t="n">
-        <v>7039087</v>
+        <v>7039023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127843091</v>
+        <v>127843080</v>
       </c>
       <c r="B2" t="n">
-        <v>97597</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222741</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445207</v>
+        <v>445269</v>
       </c>
       <c r="R2" t="n">
-        <v>7039029</v>
+        <v>7039010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843067</v>
+        <v>127843081</v>
       </c>
       <c r="B3" t="n">
-        <v>98594</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445159</v>
+        <v>445279</v>
       </c>
       <c r="R3" t="n">
-        <v>7038937</v>
+        <v>7039023</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843092</v>
+        <v>127843082</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445157</v>
+        <v>445275</v>
       </c>
       <c r="R4" t="n">
-        <v>7038934</v>
+        <v>7039024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843093</v>
+        <v>127843083</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445181</v>
+        <v>445275</v>
       </c>
       <c r="R5" t="n">
-        <v>7038904</v>
+        <v>7039025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843088</v>
+        <v>127843084</v>
       </c>
       <c r="B6" t="n">
-        <v>91470</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445253</v>
+        <v>445282</v>
       </c>
       <c r="R6" t="n">
-        <v>7039001</v>
+        <v>7039041</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843080</v>
+        <v>127843086</v>
       </c>
       <c r="B7" t="n">
-        <v>91448</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445269</v>
+        <v>445278</v>
       </c>
       <c r="R7" t="n">
-        <v>7039010</v>
+        <v>7039049</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843094</v>
+        <v>127843074</v>
       </c>
       <c r="B8" t="n">
-        <v>100753</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445285</v>
+        <v>445178</v>
       </c>
       <c r="R8" t="n">
-        <v>7039016</v>
+        <v>7038945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843090</v>
+        <v>127843070</v>
       </c>
       <c r="B9" t="n">
-        <v>97597</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445194</v>
+        <v>445248</v>
       </c>
       <c r="R9" t="n">
-        <v>7039028</v>
+        <v>7038967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1425,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843086</v>
+        <v>127843071</v>
       </c>
       <c r="B10" t="n">
-        <v>91448</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445278</v>
+        <v>445274</v>
       </c>
       <c r="R10" t="n">
-        <v>7039049</v>
+        <v>7039066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1522,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127843084</v>
+        <v>127843072</v>
       </c>
       <c r="B11" t="n">
-        <v>91448</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1569,54 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445282</v>
+        <v>445273</v>
       </c>
       <c r="R11" t="n">
-        <v>7039041</v>
+        <v>7039087</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127843082</v>
+        <v>127843067</v>
       </c>
       <c r="B12" t="n">
-        <v>91448</v>
+        <v>99142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445275</v>
+        <v>445159</v>
       </c>
       <c r="R12" t="n">
-        <v>7039024</v>
+        <v>7038937</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1772,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843083</v>
+        <v>127843092</v>
       </c>
       <c r="B13" t="n">
-        <v>91448</v>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445275</v>
+        <v>445157</v>
       </c>
       <c r="R13" t="n">
-        <v>7039025</v>
+        <v>7038934</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843095</v>
+        <v>127843093</v>
       </c>
       <c r="B14" t="n">
-        <v>100753</v>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445277</v>
+        <v>445181</v>
       </c>
       <c r="R14" t="n">
-        <v>7039062</v>
+        <v>7038904</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,65 +1966,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843072</v>
+        <v>127843094</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445273</v>
+        <v>445285</v>
       </c>
       <c r="R15" t="n">
-        <v>7039087</v>
+        <v>7039016</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843081</v>
+        <v>127843095</v>
       </c>
       <c r="B16" t="n">
-        <v>91448</v>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445279</v>
+        <v>445277</v>
       </c>
       <c r="R16" t="n">
-        <v>7039023</v>
+        <v>7039062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843070</v>
+        <v>127843090</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>98137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445248</v>
+        <v>445194</v>
       </c>
       <c r="R17" t="n">
-        <v>7038967</v>
+        <v>7039028</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2221,11 +2231,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2257,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843074</v>
+        <v>127843091</v>
       </c>
       <c r="B18" t="n">
-        <v>80217</v>
+        <v>98137</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2268,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>222741</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445178</v>
+        <v>445207</v>
       </c>
       <c r="R18" t="n">
-        <v>7038945</v>
+        <v>7039029</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,108 +2351,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>127843071</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57685</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>HStorvallen Kaxås, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>445274</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7039066</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35884-2025 artfynd.xlsx
+++ b/artfynd/A 35884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843081</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843082</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843083</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843084</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843086</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843074</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843070</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843071</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843072</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843067</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843092</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843093</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843094</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843095</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843090</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,8 +2436,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>